--- a/output/pdf_financials_xlsx/ADN.xlsx
+++ b/output/pdf_financials_xlsx/ADN.xlsx
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-2e-07</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>1.89e-05</v>
+        <v>1.91e-05</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>9.300000000000001e-06</v>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>1.89e-05</v>
+        <v>1.91e-05</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>9.300000000000001e-06</v>
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>27.83505154639175</v>
+        <v>28.12960235640648</v>
       </c>
       <c r="C30" s="3" t="n">
         <v>14.66876971608833</v>
@@ -2501,13 +2501,13 @@
         <v>0.02232</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.007601</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.007316</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.00623</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>0.001831</v>
@@ -2516,7 +2516,7 @@
         <v>0.01525</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.004808</v>
       </c>
     </row>
     <row r="35">
@@ -2617,13 +2617,13 @@
         <v>0.02232</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.007601</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.007316</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.00623</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>0.001831</v>
@@ -2632,7 +2632,7 @@
         <v>0.01525</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.004808</v>
       </c>
     </row>
     <row r="37">
@@ -3313,13 +3313,13 @@
         <v>0.00723</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.021448</v>
+        <v>0.013847</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.015806</v>
+        <v>0.008489999999999999</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.014495</v>
+        <v>0.008265</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>0.010969</v>
@@ -3328,7 +3328,7 @@
         <v>0.008576</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.013962</v>
+        <v>0.009154000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -36028,7 +36028,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E283" s="5" t="n">
@@ -37026,7 +37026,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E293" s="5" t="n">

--- a/output/pdf_financials_xlsx/ADN.xlsx
+++ b/output/pdf_financials_xlsx/ADN.xlsx
@@ -1261,13 +1261,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>1.89e-05</v>
+        <v>4.4e-05</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>9.300000000000001e-06</v>
+        <v>1.56e-05</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>8.8e-06</v>
+        <v>1.64e-05</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>0.013759</v>
@@ -1319,13 +1319,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>-2.51e-05</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-6.3e-06</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>-7.599999999999999e-06</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -2057,13 +2057,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>1.91e-05</v>
+        <v>4.42e-05</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>9.300000000000001e-06</v>
+        <v>1.56e-05</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>8.8e-06</v>
+        <v>1.64e-05</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>0.013759</v>
@@ -2173,13 +2173,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>1.91e-05</v>
+        <v>4.42e-05</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>9.300000000000001e-06</v>
+        <v>1.56e-05</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>8.8e-06</v>
+        <v>1.64e-05</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>0.014307</v>
@@ -2231,13 +2231,13 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>28.12960235640648</v>
+        <v>65.09572901325478</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>14.66876971608833</v>
+        <v>24.60567823343849</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>12.3943661971831</v>
+        <v>23.09859154929577</v>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
@@ -2317,13 +2317,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>57.04545454545455</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>40.38461538461538</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>46.34146341463415</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>0</v>
@@ -6561,7 +6561,7 @@
         <v>0</v>
       </c>
       <c r="J102" s="3" t="n">
-        <v>0</v>
+        <v>-0.000758</v>
       </c>
       <c r="K102" s="3" t="n">
         <v>0.000477</v>
@@ -6677,7 +6677,7 @@
         <v>0</v>
       </c>
       <c r="J104" s="3" t="n">
-        <v>0</v>
+        <v>-0.00087</v>
       </c>
       <c r="K104" s="3" t="n">
         <v>0.008947</v>
@@ -8559,7 +8559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U298"/>
+  <dimension ref="A1:U302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -19944,10 +19944,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M118" s="5" t="n">
+        <v>-0.0006089999999999999</v>
       </c>
       <c r="N118" s="5" t="n">
         <v>0.004743</v>
@@ -20510,10 +20508,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M124" s="5" t="n">
+        <v>-0.016731</v>
       </c>
       <c r="N124" s="5" t="n">
         <v>-0.017986</v>
@@ -21321,10 +21317,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M133" s="5" t="n">
+        <v>0.001021</v>
       </c>
       <c r="N133" s="5" t="n">
         <v>-0.004055</v>
@@ -21511,10 +21505,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M135" s="5" t="n">
+        <v>-0.00087</v>
       </c>
       <c r="N135" s="5" t="n">
         <v>0.008947</v>
@@ -21598,10 +21590,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M136" s="5" t="n">
+        <v>-2e-06</v>
       </c>
       <c r="N136" s="5" t="n">
         <v>-0.000626</v>
@@ -22051,15 +22041,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M141" s="5" t="n">
+        <v>-0.002856</v>
+      </c>
+      <c r="N141" s="5" t="n">
+        <v>-0.006301</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
@@ -22156,10 +22142,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M142" s="5" t="n">
+        <v>-0.000758</v>
       </c>
       <c r="N142" s="5" t="n">
         <v>0.000477</v>
@@ -22208,7 +22192,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -22249,10 +22237,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M143" s="5" t="n">
+        <v>0.005121</v>
       </c>
       <c r="N143" s="5" t="n">
         <v>0.003564</v>
@@ -23702,10 +23688,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M158" s="5" t="n">
+        <v>-0.000283</v>
       </c>
       <c r="N158" s="5" t="n">
         <v>-0.000943</v>
@@ -24058,10 +24042,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Deferred income tax expense 12</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -24082,25 +24070,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I162" s="5" t="n">
-        <v>0.003311</v>
-      </c>
-      <c r="J162" s="5" t="n">
-        <v>0.004004</v>
-      </c>
-      <c r="K162" s="5" t="n">
-        <v>0.019414</v>
-      </c>
-      <c r="L162" s="5" t="n">
-        <v>0.005414</v>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M162" s="5" t="n">
-        <v>0.005121</v>
-      </c>
-      <c r="N162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000502</v>
+      </c>
+      <c r="N162" s="5" t="n">
+        <v>0.000313</v>
       </c>
       <c r="O162" t="inlineStr">
         <is>
@@ -24151,14 +24145,10 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Depreciation 5</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Fair value adjustments</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
@@ -24174,34 +24164,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K163" s="5" t="n">
-        <v>0.000535</v>
-      </c>
-      <c r="L163" s="5" t="n">
-        <v>0.000515</v>
+      <c r="H163" s="5" t="n">
+        <v>-0.013501</v>
+      </c>
+      <c r="I163" s="5" t="n">
+        <v>-0.001924</v>
+      </c>
+      <c r="J163" s="5" t="n">
+        <v>-0.002633</v>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M163" s="5" t="n">
-        <v>0.000502</v>
-      </c>
-      <c r="N163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000705</v>
+      </c>
+      <c r="N163" s="5" t="n">
+        <v>-0.009327</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
@@ -24247,12 +24233,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Adjustments to net income</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Fair value adjustments 4</t>
+          <t>Increase in cash and cash equivalents during the year</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -24276,27 +24262,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I164" s="5" t="n">
+        <v>0.002117</v>
       </c>
       <c r="J164" s="5" t="n">
-        <v>-0.002633</v>
+        <v>0.002428</v>
       </c>
       <c r="K164" s="5" t="n">
-        <v>-0.045979</v>
+        <v>0.004096</v>
       </c>
       <c r="L164" s="5" t="n">
-        <v>-0.013168</v>
+        <v>0.005056</v>
       </c>
       <c r="M164" s="5" t="n">
-        <v>0.000705</v>
-      </c>
-      <c r="N164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.001938</v>
+      </c>
+      <c r="N164" s="5" t="n">
+        <v>0.004297</v>
       </c>
       <c r="O164" t="inlineStr">
         <is>
@@ -24347,10 +24329,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Unrealized exchange (gain) / loss on long-term debt 6</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr"/>
+          <t>Deferred income tax expense 12</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
@@ -24371,26 +24357,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I165" s="5" t="n">
+        <v>0.003311</v>
+      </c>
+      <c r="J165" s="5" t="n">
+        <v>0.004004</v>
+      </c>
+      <c r="K165" s="5" t="n">
+        <v>0.019414</v>
       </c>
       <c r="L165" s="5" t="n">
-        <v>0.016095</v>
+        <v>0.005414</v>
       </c>
       <c r="M165" s="5" t="n">
-        <v>-0.002856</v>
+        <v>0.005121</v>
       </c>
       <c r="N165" t="inlineStr">
         <is>
@@ -24446,10 +24426,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Interest expense, net</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr"/>
+          <t>Depreciation 5</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -24465,23 +24449,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H166" s="5" t="n">
-        <v>0.003157</v>
-      </c>
-      <c r="I166" s="5" t="n">
-        <v>0.002889</v>
-      </c>
-      <c r="J166" s="5" t="n">
-        <v>0.003032</v>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K166" s="5" t="n">
-        <v>0.003203</v>
+        <v>0.000535</v>
       </c>
       <c r="L166" s="5" t="n">
-        <v>0.003364</v>
+        <v>0.000515</v>
       </c>
       <c r="M166" s="5" t="n">
-        <v>0.002942</v>
+        <v>0.000502</v>
       </c>
       <c r="N166" t="inlineStr">
         <is>
@@ -24537,7 +24527,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Interest paid, net</t>
+          <t>Fair value adjustments 4</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
@@ -24556,23 +24546,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H167" s="5" t="n">
-        <v>-0.003047</v>
-      </c>
-      <c r="I167" s="5" t="n">
-        <v>-0.002199</v>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J167" s="5" t="n">
-        <v>-0.003052</v>
+        <v>-0.002633</v>
       </c>
       <c r="K167" s="5" t="n">
-        <v>-0.003223</v>
+        <v>-0.045979</v>
       </c>
       <c r="L167" s="5" t="n">
-        <v>-0.003463</v>
+        <v>-0.013168</v>
       </c>
       <c r="M167" s="5" t="n">
-        <v>-0.002836</v>
+        <v>0.000705</v>
       </c>
       <c r="N167" t="inlineStr">
         <is>
@@ -24628,7 +24622,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Loss on disposal of land, roads and other fixed assets</t>
+          <t>Unrealized exchange (gain) / loss on long-term debt 6</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
@@ -24662,16 +24656,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K168" s="5" t="n">
-        <v>0.00021</v>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L168" s="5" t="n">
-        <v>6e-06</v>
-      </c>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.016095</v>
+      </c>
+      <c r="M168" s="5" t="n">
+        <v>-0.002856</v>
       </c>
       <c r="N168" t="inlineStr">
         <is>
@@ -24727,7 +24721,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Other, net</t>
+          <t>Interest expense, net</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
@@ -24746,27 +24740,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H169" s="5" t="n">
+        <v>0.003157</v>
+      </c>
+      <c r="I169" s="5" t="n">
+        <v>0.002889</v>
       </c>
       <c r="J169" s="5" t="n">
-        <v>0.000219</v>
+        <v>0.003032</v>
       </c>
       <c r="K169" s="5" t="n">
-        <v>0.000457</v>
+        <v>0.003203</v>
       </c>
       <c r="L169" s="5" t="n">
-        <v>0.001691</v>
+        <v>0.003364</v>
       </c>
       <c r="M169" s="5" t="n">
-        <v>-0.000108</v>
+        <v>0.002942</v>
       </c>
       <c r="N169" t="inlineStr">
         <is>
@@ -24822,14 +24812,10 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Net change in non-cash working capital 16</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>ChangeInWorkingCapital</t>
-        </is>
-      </c>
+          <t>Interest paid, net</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
@@ -24845,27 +24831,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H170" s="5" t="n">
+        <v>-0.003047</v>
+      </c>
+      <c r="I170" s="5" t="n">
+        <v>-0.002199</v>
       </c>
       <c r="J170" s="5" t="n">
-        <v>0.002212</v>
+        <v>-0.003052</v>
       </c>
       <c r="K170" s="5" t="n">
-        <v>-0.000191</v>
+        <v>-0.003223</v>
       </c>
       <c r="L170" s="5" t="n">
-        <v>-0.003401</v>
+        <v>-0.003463</v>
       </c>
       <c r="M170" s="5" t="n">
-        <v>-0.000607</v>
+        <v>-0.002836</v>
       </c>
       <c r="N170" t="inlineStr">
         <is>
@@ -24916,12 +24898,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Adjustments to net income</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Deferred financing costs</t>
+          <t>Loss on disposal of land, roads and other fixed assets</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
@@ -24955,13 +24937,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K171" s="5" t="n">
+        <v>0.00021</v>
       </c>
       <c r="L171" s="5" t="n">
-        <v>-0.000502</v>
+        <v>6e-06</v>
       </c>
       <c r="M171" t="inlineStr">
         <is>
@@ -25017,12 +24997,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Adjustments to net income</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Dividends paid to shareholders 14</t>
+          <t>Other, net</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
@@ -25031,29 +25011,37 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F172" s="5" t="n">
-        <v>-1.22e-05</v>
-      </c>
-      <c r="G172" s="5" t="n">
-        <v>-2.8e-06</v>
-      </c>
-      <c r="H172" s="5" t="n">
-        <v>-0.01119</v>
-      </c>
-      <c r="I172" s="5" t="n">
-        <v>-0.013804</v>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J172" s="5" t="n">
-        <v>-0.013804</v>
+        <v>0.000219</v>
       </c>
       <c r="K172" s="5" t="n">
-        <v>-0.013804</v>
+        <v>0.000457</v>
       </c>
       <c r="L172" s="5" t="n">
-        <v>-0.014744</v>
+        <v>0.001691</v>
       </c>
       <c r="M172" s="5" t="n">
-        <v>-0.016731</v>
+        <v>-0.000108</v>
       </c>
       <c r="N172" t="inlineStr">
         <is>
@@ -25104,15 +25092,19 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Adjustments to net income</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Additions to timber, land, roads and other fixed assets 5</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
+          <t>Net change in non-cash working capital 16</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -25138,19 +25130,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J173" s="5" t="n">
+        <v>0.002212</v>
       </c>
       <c r="K173" s="5" t="n">
-        <v>-0.000318</v>
+        <v>-0.000191</v>
       </c>
       <c r="L173" s="5" t="n">
-        <v>-0.000405</v>
+        <v>-0.003401</v>
       </c>
       <c r="M173" s="5" t="n">
-        <v>-0.000283</v>
+        <v>-0.000607</v>
       </c>
       <c r="N173" t="inlineStr">
         <is>
@@ -25201,12 +25191,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Increase in cash and cash equivalents during the year</t>
+          <t>Deferred financing costs</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -25230,20 +25220,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I174" s="5" t="n">
-        <v>0.002117</v>
-      </c>
-      <c r="J174" s="5" t="n">
-        <v>0.002428</v>
-      </c>
-      <c r="K174" s="5" t="n">
-        <v>0.004096</v>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L174" s="5" t="n">
-        <v>0.005056</v>
-      </c>
-      <c r="M174" s="5" t="n">
-        <v>0.001938</v>
+        <v>-0.000502</v>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N174" t="inlineStr">
         <is>
@@ -25294,12 +25292,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Adjustments to net income</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Gain on revaluation of land and roads 5</t>
+          <t>Dividends paid to shareholders 14</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
@@ -25308,43 +25306,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F175" s="5" t="n">
+        <v>-1.22e-05</v>
+      </c>
+      <c r="G175" s="5" t="n">
+        <v>-2.8e-06</v>
+      </c>
+      <c r="H175" s="5" t="n">
+        <v>-0.01119</v>
+      </c>
+      <c r="I175" s="5" t="n">
+        <v>-0.013804</v>
+      </c>
+      <c r="J175" s="5" t="n">
+        <v>-0.013804</v>
       </c>
       <c r="K175" s="5" t="n">
-        <v>-0.006665</v>
-      </c>
-      <c r="L175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.013804</v>
+      </c>
+      <c r="L175" s="5" t="n">
+        <v>-0.014744</v>
+      </c>
+      <c r="M175" s="5" t="n">
+        <v>-0.016731</v>
       </c>
       <c r="N175" t="inlineStr">
         <is>
@@ -25395,12 +25379,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Adjustments to net income</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Unrealized exchange loss on long-term debt 6</t>
+          <t>Additions to timber, land, roads and other fixed assets 5</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
@@ -25435,15 +25419,13 @@
         </is>
       </c>
       <c r="K176" s="5" t="n">
-        <v>0.007214</v>
+        <v>-0.000318</v>
       </c>
       <c r="L176" s="5" t="n">
-        <v>0.016095</v>
-      </c>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.000405</v>
+      </c>
+      <c r="M176" s="5" t="n">
+        <v>-0.000283</v>
       </c>
       <c r="N176" t="inlineStr">
         <is>
@@ -25499,14 +25481,10 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 5</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>DepreciationAndAmortization</t>
-        </is>
-      </c>
+          <t>Gain on revaluation of land and roads 5</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -25522,17 +25500,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H177" s="5" t="n">
-        <v>0.000548</v>
-      </c>
-      <c r="I177" s="5" t="n">
-        <v>0.000548</v>
-      </c>
-      <c r="J177" s="5" t="n">
-        <v>0.000566</v>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K177" s="5" t="n">
-        <v>0.000535</v>
+        <v>-0.006665</v>
       </c>
       <c r="L177" t="inlineStr">
         <is>
@@ -25598,7 +25582,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Loss / (gain) on revaluation of roads and land 5</t>
+          <t>Unrealized exchange loss on long-term debt 6</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -25627,16 +25611,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J178" s="5" t="n">
-        <v>0.000134</v>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K178" s="5" t="n">
-        <v>-0.006665</v>
-      </c>
-      <c r="L178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.007214</v>
+      </c>
+      <c r="L178" s="5" t="n">
+        <v>0.016095</v>
       </c>
       <c r="M178" t="inlineStr">
         <is>
@@ -25697,10 +25681,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Unrealized exchange loss on long term debt 6</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr"/>
+          <t>Depreciation and amortization 5</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -25716,21 +25704,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H179" s="5" t="n">
+        <v>0.000548</v>
+      </c>
+      <c r="I179" s="5" t="n">
+        <v>0.000548</v>
       </c>
       <c r="J179" s="5" t="n">
-        <v>0.005078</v>
+        <v>0.000566</v>
       </c>
       <c r="K179" s="5" t="n">
-        <v>0.007214</v>
+        <v>0.000535</v>
       </c>
       <c r="L179" t="inlineStr">
         <is>
@@ -25796,7 +25780,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Fair value adjustments</t>
+          <t>Loss / (gain) on revaluation of roads and land 5</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
@@ -25815,19 +25799,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H180" s="5" t="n">
-        <v>-0.013501</v>
-      </c>
-      <c r="I180" s="5" t="n">
-        <v>-0.001924</v>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J180" s="5" t="n">
-        <v>-0.002633</v>
-      </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000134</v>
+      </c>
+      <c r="K180" s="5" t="n">
+        <v>-0.006665</v>
       </c>
       <c r="L180" t="inlineStr">
         <is>
@@ -25893,7 +25879,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Loss on revaluation of roads and land 5</t>
+          <t>Unrealized exchange loss on long term debt 6</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -25912,19 +25898,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H181" s="5" t="n">
-        <v>0.001527</v>
-      </c>
-      <c r="I181" s="5" t="n">
-        <v>8.3e-05</v>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J181" s="5" t="n">
-        <v>0.000134</v>
-      </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.005078</v>
+      </c>
+      <c r="K181" s="5" t="n">
+        <v>0.007214</v>
       </c>
       <c r="L181" t="inlineStr">
         <is>
@@ -25990,7 +25978,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Unrealized exchange (gain) loss on long term debt 6</t>
+          <t>Loss on revaluation of roads and land 5</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
@@ -26009,16 +25997,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H182" s="5" t="n">
+        <v>0.001527</v>
       </c>
       <c r="I182" s="5" t="n">
-        <v>-0.002148</v>
+        <v>8.3e-05</v>
       </c>
       <c r="J182" s="5" t="n">
-        <v>0.005078</v>
+        <v>0.000134</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
@@ -26089,7 +26075,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Deferred tax expense 12</t>
+          <t>Unrealized exchange (gain) loss on long term debt 6</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
@@ -26108,16 +26094,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H183" s="5" t="n">
-        <v>0.006564</v>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I183" s="5" t="n">
-        <v>0.003311</v>
-      </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.002148</v>
+      </c>
+      <c r="J183" s="5" t="n">
+        <v>0.005078</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
@@ -26188,10 +26174,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Unrealized exchange gain/(loss) on long term debt</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr"/>
+          <t>Deferred tax expense 12</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
@@ -26208,10 +26198,10 @@
         </is>
       </c>
       <c r="H184" s="5" t="n">
-        <v>0.003473</v>
+        <v>0.006564</v>
       </c>
       <c r="I184" s="5" t="n">
-        <v>-0.002148</v>
+        <v>0.003311</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
@@ -26282,12 +26272,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Adjustments to net income</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Borrowing of term facility</t>
+          <t>Unrealized exchange gain/(loss) on long term debt</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -26307,12 +26297,10 @@
         </is>
       </c>
       <c r="H185" s="5" t="n">
-        <v>0.070608</v>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.003473</v>
+      </c>
+      <c r="I185" s="5" t="n">
+        <v>-0.002148</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
@@ -26388,7 +26376,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Repayment of bank term credit facility and term loan 6</t>
+          <t>Borrowing of term facility</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -26408,7 +26396,7 @@
         </is>
       </c>
       <c r="H186" s="5" t="n">
-        <v>-0.073639</v>
+        <v>0.070608</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
@@ -26489,7 +26477,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Deferred financing costs 6</t>
+          <t>Repayment of bank term credit facility and term loan 6</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
@@ -26509,7 +26497,7 @@
         </is>
       </c>
       <c r="H187" s="5" t="n">
-        <v>-0.001205</v>
+        <v>-0.073639</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
@@ -26585,12 +26573,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Increase (decrease) in cash and cash equivalents during the year</t>
+          <t>Deferred financing costs 6</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
@@ -26610,10 +26598,12 @@
         </is>
       </c>
       <c r="H188" s="5" t="n">
-        <v>-0.003314</v>
-      </c>
-      <c r="I188" s="5" t="n">
-        <v>0.002117</v>
+        <v>-0.001205</v>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
@@ -26682,10 +26672,14 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr"/>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>For the Years Ended December</t>
+          <t>Increase (decrease) in cash and cash equivalents during the year</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
@@ -26705,12 +26699,10 @@
         </is>
       </c>
       <c r="H189" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.003314</v>
+      </c>
+      <c r="I189" s="5" t="n">
+        <v>0.002117</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
@@ -26782,7 +26774,7 @@
       <c r="B190" t="inlineStr"/>
       <c r="C190" t="inlineStr">
         <is>
-          <t>(CAD thousands) Note 2011</t>
+          <t>For the Years Ended December</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
@@ -26802,7 +26794,7 @@
         </is>
       </c>
       <c r="H190" s="5" t="n">
-        <v>0.020101</v>
+        <v>3.1e-05</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
@@ -26876,21 +26868,13 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Operating activities</t>
-        </is>
-      </c>
+      <c r="B191" t="inlineStr"/>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Net income $ 13,759 $</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+          <t>(CAD thousands) Note 2011</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
@@ -26907,7 +26891,7 @@
         </is>
       </c>
       <c r="H191" s="5" t="n">
-        <v>0.031306</v>
+        <v>0.020101</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
@@ -26983,15 +26967,19 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Adjustments to net income</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Deferred income tax expense 13 6,564</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr"/>
+          <t>Net income $ 13,759 $</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
@@ -27008,7 +26996,7 @@
         </is>
       </c>
       <c r="H192" s="5" t="n">
-        <v>0.00221</v>
+        <v>0.031306</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
@@ -27089,12 +27077,12 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 6 548</t>
+          <t>Deferred income tax expense 13 6,564</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>DeferredTax</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -27113,7 +27101,7 @@
         </is>
       </c>
       <c r="H193" s="5" t="n">
-        <v>0.000499</v>
+        <v>0.00221</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
@@ -27194,10 +27182,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Fair value adjustments (13,501)</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr"/>
+          <t>Depreciation and amortization 6 548</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -27214,7 +27206,7 @@
         </is>
       </c>
       <c r="H194" s="5" t="n">
-        <v>-0.00395</v>
+        <v>0.000499</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
@@ -27295,7 +27287,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Loss on revaluation of roads and land 6 1,527</t>
+          <t>Fair value adjustments (13,501)</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
@@ -27315,7 +27307,7 @@
         </is>
       </c>
       <c r="H195" s="5" t="n">
-        <v>0.005005</v>
+        <v>-0.00395</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
@@ -27396,7 +27388,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Unrealized exchange loss on long term debt 3,473</t>
+          <t>Loss on revaluation of roads and land 6 1,527</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
@@ -27415,10 +27407,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H196" s="5" t="n">
+        <v>0.005005</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
@@ -27499,7 +27489,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Interest expense, net 3,157</t>
+          <t>Unrealized exchange loss on long term debt 3,473</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
@@ -27518,8 +27508,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H197" s="5" t="n">
-        <v>0.003791</v>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
@@ -27600,7 +27592,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Interest paid, net (3,047)</t>
+          <t>Interest expense, net 3,157</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
@@ -27620,7 +27612,7 @@
         </is>
       </c>
       <c r="H198" s="5" t="n">
-        <v>-0.003791</v>
+        <v>0.003791</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
@@ -27701,7 +27693,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Gain on sale of timberlands (107)</t>
+          <t>Interest paid, net (3,047)</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
@@ -27721,7 +27713,7 @@
         </is>
       </c>
       <c r="H199" s="5" t="n">
-        <v>-4e-05</v>
+        <v>-0.003791</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
@@ -27802,7 +27794,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Gain on corporate conversion 4 —</t>
+          <t>Gain on sale of timberlands (107)</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
@@ -27822,7 +27814,7 @@
         </is>
       </c>
       <c r="H200" s="5" t="n">
-        <v>-0.021086</v>
+        <v>-4e-05</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
@@ -27903,7 +27895,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Net change in non-cash working capital balances and other (325)</t>
+          <t>Gain on corporate conversion 4 —</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
@@ -27923,7 +27915,7 @@
         </is>
       </c>
       <c r="H201" s="5" t="n">
-        <v>8.7e-05</v>
+        <v>-0.021086</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
@@ -27999,12 +27991,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Adjustments to net income</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Borrowing of term facility 70,608</t>
+          <t>Net change in non-cash working capital balances and other (325)</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
@@ -28023,10 +28015,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H202" s="5" t="n">
+        <v>8.7e-05</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
@@ -28107,7 +28097,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Repayment of bank term credit facility and term loan 7 (73,639)</t>
+          <t>Borrowing of term facility 70,608</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
@@ -28210,7 +28200,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Repayment of revolving facility 7 —</t>
+          <t>Repayment of bank term credit facility and term loan 7 (73,639)</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
@@ -28229,8 +28219,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H204" s="5" t="n">
-        <v>-0.0055</v>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
@@ -28311,7 +28303,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Deferred financing costs 7 (1,205)</t>
+          <t>Repayment of revolving facility 7 —</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
@@ -28331,7 +28323,7 @@
         </is>
       </c>
       <c r="H205" s="5" t="n">
-        <v>-7.3e-05</v>
+        <v>-0.0055</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
@@ -28412,7 +28404,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Dividends paid to shareholders 15 (11,190)</t>
+          <t>Deferred financing costs 7 (1,205)</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -28432,7 +28424,7 @@
         </is>
       </c>
       <c r="H206" s="5" t="n">
-        <v>-0.002788</v>
+        <v>-7.3e-05</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
@@ -28508,12 +28500,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Additions to timber, land, roads and other fixed assets (45)</t>
+          <t>Dividends paid to shareholders 15 (11,190)</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -28533,7 +28525,7 @@
         </is>
       </c>
       <c r="H207" s="5" t="n">
-        <v>-0.00043</v>
+        <v>-0.002788</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
@@ -28614,7 +28606,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Proceeds from sale of timberlands 109</t>
+          <t>Additions to timber, land, roads and other fixed assets (45)</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
@@ -28634,7 +28626,7 @@
         </is>
       </c>
       <c r="H208" s="5" t="n">
-        <v>4e-05</v>
+        <v>-0.00043</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
@@ -28715,7 +28707,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Increase in cash and cash equivalents during the year (3,314)</t>
+          <t>Proceeds from sale of timberlands 109</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
@@ -28735,7 +28727,7 @@
         </is>
       </c>
       <c r="H209" s="5" t="n">
-        <v>0.00528</v>
+        <v>4e-05</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
@@ -28816,14 +28808,10 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of year 7,333</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Increase in cash and cash equivalents during the year (3,314)</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>
@@ -28840,7 +28828,7 @@
         </is>
       </c>
       <c r="H210" s="5" t="n">
-        <v>0.002053</v>
+        <v>0.00528</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
@@ -28921,12 +28909,12 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of year $ 4,019 $</t>
+          <t>Cash and cash equivalents, beginning of year 7,333</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -28945,7 +28933,7 @@
         </is>
       </c>
       <c r="H211" s="5" t="n">
-        <v>0.007333</v>
+        <v>0.002053</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
@@ -29021,30 +29009,36 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Future income tax recovery 12</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr"/>
+          <t>Cash and cash equivalents, end of year $ 4,019 $</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E212" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F212" s="5" t="n">
-        <v>-3e-06</v>
-      </c>
-      <c r="G212" s="5" t="n">
-        <v>-1.2e-06</v>
-      </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H212" s="5" t="n">
+        <v>0.007333</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
@@ -29125,18 +29119,24 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Depreciation and depletion</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr"/>
-      <c r="E213" s="5" t="n">
-        <v>7.4e-06</v>
+          <t>Future income tax recovery 12</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F213" s="5" t="n">
-        <v>7.1e-06</v>
+        <v>-3e-06</v>
       </c>
       <c r="G213" s="5" t="n">
-        <v>6.599999999999999e-06</v>
+        <v>-1.2e-06</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -29222,20 +29222,18 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Gain on sale of timberlands 8</t>
+          <t>Depreciation and depletion</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
       <c r="E214" s="5" t="n">
-        <v>-7e-07</v>
+        <v>7.4e-06</v>
       </c>
       <c r="F214" s="5" t="n">
-        <v>-6e-07</v>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7.1e-06</v>
+      </c>
+      <c r="G214" s="5" t="n">
+        <v>6.599999999999999e-06</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -29321,15 +29319,15 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Gain on Class B Interest Liability of a subsidiary 6</t>
+          <t>Gain on sale of timberlands 8</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
       <c r="E215" s="5" t="n">
-        <v>-2.22e-05</v>
+        <v>-7e-07</v>
       </c>
       <c r="F215" s="5" t="n">
-        <v>-4.7e-06</v>
+        <v>-6e-07</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
@@ -29420,18 +29418,20 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Items not affecting cash total</t>
+          <t>Gain on Class B Interest Liability of a subsidiary 6</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
       <c r="E216" s="5" t="n">
-        <v>9.6e-06</v>
+        <v>-2.22e-05</v>
       </c>
       <c r="F216" s="5" t="n">
-        <v>8.1e-06</v>
-      </c>
-      <c r="G216" s="5" t="n">
-        <v>1.42e-05</v>
+        <v>-4.7e-06</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -29517,20 +29517,18 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Net change in non-cash working capital balances and other</t>
+          <t>Items not affecting cash total</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
       <c r="E217" s="5" t="n">
-        <v>4.5e-06</v>
+        <v>9.6e-06</v>
       </c>
       <c r="F217" s="5" t="n">
-        <v>-4e-06</v>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>8.1e-06</v>
+      </c>
+      <c r="G217" s="5" t="n">
+        <v>1.42e-05</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -29611,22 +29609,20 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Proceeds from sale of timberlands 8</t>
+          <t>Net change in non-cash working capital balances and other</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E218" s="5" t="n">
+        <v>4.5e-06</v>
       </c>
       <c r="F218" s="5" t="n">
-        <v>6e-07</v>
+        <v>-4e-06</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
@@ -29717,18 +29713,22 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Additions to Timberlands, logging roads and ﬁ xed assets 8</t>
+          <t>Proceeds from sale of timberlands 8</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
-      <c r="E219" s="5" t="n">
-        <v>-5e-07</v>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F219" s="5" t="n">
-        <v>-8.000000000000001e-07</v>
-      </c>
-      <c r="G219" s="5" t="n">
-        <v>-4e-07</v>
+        <v>6e-07</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -29814,18 +29814,18 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Silviculture expenditures</t>
+          <t>Additions to Timberlands, logging roads and ﬁ xed assets 8</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
       <c r="E220" s="5" t="n">
-        <v>-3e-07</v>
+        <v>-5e-07</v>
       </c>
       <c r="F220" s="5" t="n">
-        <v>-1e-07</v>
+        <v>-8.000000000000001e-07</v>
       </c>
       <c r="G220" s="5" t="n">
-        <v>-2e-07</v>
+        <v>-4e-07</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -29911,22 +29911,18 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Issuance of note receivable 3</t>
+          <t>Silviculture expenditures</t>
         </is>
       </c>
       <c r="D221" t="inlineStr"/>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E221" s="5" t="n">
+        <v>-3e-07</v>
       </c>
       <c r="F221" s="5" t="n">
-        <v>-4e-06</v>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1e-07</v>
+      </c>
+      <c r="G221" s="5" t="n">
+        <v>-2e-07</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -30007,12 +30003,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Borrowing (repayment) on revolving credit facility 5</t>
+          <t>Issuance of note receivable 3</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
@@ -30022,10 +30018,12 @@
         </is>
       </c>
       <c r="F222" s="5" t="n">
-        <v>5.5e-06</v>
-      </c>
-      <c r="G222" s="5" t="n">
-        <v>-5.5e-06</v>
+        <v>-4e-06</v>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -30111,18 +30109,20 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Increase (decrease) in cash and cash equivalents during the year</t>
+          <t>Borrowing (repayment) on revolving credit facility 5</t>
         </is>
       </c>
       <c r="D223" t="inlineStr"/>
-      <c r="E223" s="5" t="n">
-        <v>4.1e-06</v>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F223" s="5" t="n">
-        <v>-6.9e-06</v>
+        <v>5.5e-06</v>
       </c>
       <c r="G223" s="5" t="n">
-        <v>5.2e-06</v>
+        <v>-5.5e-06</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -30208,22 +30208,18 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of year</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Increase (decrease) in cash and cash equivalents during the year</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr"/>
       <c r="E224" s="5" t="n">
-        <v>4.900000000000001e-06</v>
+        <v>4.1e-06</v>
       </c>
       <c r="F224" s="5" t="n">
-        <v>9e-06</v>
+        <v>-6.9e-06</v>
       </c>
       <c r="G224" s="5" t="n">
-        <v>2.1e-06</v>
+        <v>5.2e-06</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -30309,22 +30305,22 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of year $</t>
+          <t>Cash and cash equivalents, beginning of year</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E225" s="5" t="n">
+        <v>4.900000000000001e-06</v>
+      </c>
+      <c r="F225" s="5" t="n">
         <v>9e-06</v>
       </c>
-      <c r="F225" s="5" t="n">
+      <c r="G225" s="5" t="n">
         <v>2.1e-06</v>
-      </c>
-      <c r="G225" s="5" t="n">
-        <v>7.3e-06</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -30410,24 +30406,22 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Cash interest paid</t>
+          <t>Cash and cash equivalents, end of year $</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>InterestPaidSupplementalData</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E226" s="5" t="n">
+        <v>9e-06</v>
       </c>
       <c r="F226" s="5" t="n">
-        <v>3.4e-06</v>
+        <v>2.1e-06</v>
       </c>
       <c r="G226" s="5" t="n">
-        <v>3.8e-06</v>
+        <v>7.3e-06</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
@@ -30508,25 +30502,29 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Future income tax expense (recovery) 12</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr"/>
-      <c r="E227" s="5" t="n">
-        <v>6.2e-06</v>
+          <t>Cash interest paid</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>InterestPaidSupplementalData</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F227" s="5" t="n">
-        <v>-3e-06</v>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.4e-06</v>
+      </c>
+      <c r="G227" s="5" t="n">
+        <v>3.8e-06</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
@@ -30607,20 +30605,20 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Sale of timberlands, logging roads and ﬁ xed assets 8</t>
+          <t>Future income tax expense (recovery) 12</t>
         </is>
       </c>
       <c r="D228" t="inlineStr"/>
       <c r="E228" s="5" t="n">
-        <v>8.000000000000001e-07</v>
+        <v>6.2e-06</v>
       </c>
       <c r="F228" s="5" t="n">
-        <v>6e-07</v>
+        <v>-3e-06</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
@@ -30711,17 +30709,15 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Issuance of note receivable 15</t>
+          <t>Sale of timberlands, logging roads and ﬁ xed assets 8</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E229" s="5" t="n">
+        <v>8.000000000000001e-07</v>
       </c>
       <c r="F229" s="5" t="n">
-        <v>-4e-06</v>
+        <v>6e-07</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
@@ -30807,20 +30803,22 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Distributions paid to unitholders 14</t>
+          <t>Issuance of note receivable 15</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
-      <c r="E230" s="5" t="n">
-        <v>-1e-05</v>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F230" s="5" t="n">
-        <v>-1.22e-05</v>
+        <v>-4e-06</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
@@ -30911,17 +30909,15 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Borrowing from revolving credit facility 5</t>
+          <t>Distributions paid to unitholders 14</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E231" s="5" t="n">
+        <v>-1e-05</v>
       </c>
       <c r="F231" s="5" t="n">
-        <v>5.5e-06</v>
+        <v>-1.22e-05</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
@@ -31002,76 +30998,102 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Net income $</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Borrowing from revolving credit facility 5</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F232" s="5" t="n">
+        <v>5.5e-06</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H232" s="5" t="n">
-        <v>0.013759</v>
-      </c>
-      <c r="I232" s="5" t="n">
-        <v>0.013729</v>
-      </c>
-      <c r="J232" s="5" t="n">
-        <v>0.007248</v>
-      </c>
-      <c r="K232" s="5" t="n">
-        <v>0.043238</v>
-      </c>
-      <c r="L232" s="5" t="n">
-        <v>0.013641</v>
-      </c>
-      <c r="M232" s="5" t="n">
-        <v>0.016072</v>
-      </c>
-      <c r="N232" s="5" t="n">
-        <v>0.030819</v>
-      </c>
-      <c r="O232" s="5" t="n">
-        <v>0.026264</v>
-      </c>
-      <c r="P232" s="5" t="n">
-        <v>0.017325</v>
-      </c>
-      <c r="Q232" s="5" t="n">
-        <v>0.018684</v>
-      </c>
-      <c r="R232" s="5" t="n">
-        <v>0.035507</v>
-      </c>
-      <c r="S232" s="5" t="n">
-        <v>0.029434</v>
-      </c>
-      <c r="T232" s="5" t="n">
-        <v>0.021738</v>
-      </c>
-      <c r="U232" s="5" t="n">
-        <v>0.048973</v>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="233">
@@ -31080,17 +31102,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>Other comprehensive income / (loss)</t>
-        </is>
-      </c>
+      <c r="B233" t="inlineStr"/>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Gain / (loss) on revaluation of land and roads, net of deferred income tax expense / (recovery) of $(5,792)</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr"/>
+          <t>Net income $</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -31106,71 +31128,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H233" s="5" t="n">
+        <v>0.013759</v>
+      </c>
+      <c r="I233" s="5" t="n">
+        <v>0.013729</v>
+      </c>
+      <c r="J233" s="5" t="n">
+        <v>0.007248</v>
+      </c>
+      <c r="K233" s="5" t="n">
+        <v>0.043238</v>
+      </c>
+      <c r="L233" s="5" t="n">
+        <v>0.013641</v>
+      </c>
+      <c r="M233" s="5" t="n">
+        <v>0.016072</v>
+      </c>
+      <c r="N233" s="5" t="n">
+        <v>0.030819</v>
+      </c>
+      <c r="O233" s="5" t="n">
+        <v>0.026264</v>
+      </c>
+      <c r="P233" s="5" t="n">
+        <v>0.017325</v>
+      </c>
+      <c r="Q233" s="5" t="n">
+        <v>0.018684</v>
+      </c>
+      <c r="R233" s="5" t="n">
+        <v>0.035507</v>
+      </c>
+      <c r="S233" s="5" t="n">
+        <v>0.029434</v>
       </c>
       <c r="T233" s="5" t="n">
-        <v>0.004799</v>
+        <v>0.021738</v>
       </c>
       <c r="U233" s="5" t="n">
-        <v>-0.014321</v>
+        <v>0.048973</v>
       </c>
     </row>
     <row r="234">
@@ -31186,7 +31184,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Other comprehensive income / (loss) total</t>
+          <t>Gain / (loss) on revaluation of land and roads, net of deferred income tax expense / (recovery) of $(5,792)</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -31235,11 +31233,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N234" s="5" t="n">
-        <v>-0.006181</v>
-      </c>
-      <c r="O234" s="5" t="n">
-        <v>0.007402</v>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P234" t="inlineStr">
         <is>
@@ -31256,16 +31258,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S234" s="5" t="n">
-        <v>0.002522</v>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T234" s="5" t="n">
-        <v>0.001706</v>
-      </c>
-      <c r="U234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.004799</v>
+      </c>
+      <c r="U234" s="5" t="n">
+        <v>-0.014321</v>
       </c>
     </row>
     <row r="235">
@@ -31276,12 +31278,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Unrealized foreign currency translation gain / (loss), net</t>
+          <t>Other comprehensive income / (loss)</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Unrealized foreign currency translation gain / (loss), net of deferred income tax recovery of $nil (2024 – 13</t>
+          <t>Other comprehensive income / (loss) total</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -31330,15 +31332,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N235" s="5" t="n">
+        <v>-0.006181</v>
+      </c>
+      <c r="O235" s="5" t="n">
+        <v>0.007402</v>
       </c>
       <c r="P235" t="inlineStr">
         <is>
@@ -31355,16 +31353,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S235" s="5" t="n">
+        <v>0.002522</v>
       </c>
       <c r="T235" s="5" t="n">
-        <v>0.00512</v>
-      </c>
-      <c r="U235" s="5" t="n">
-        <v>-0.003421</v>
+        <v>0.001706</v>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="236">
@@ -31375,12 +31373,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>deferred income tax expense of $369)</t>
+          <t>Unrealized foreign currency translation gain / (loss), net</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>deferred income tax expense of $369) total</t>
+          <t>Unrealized foreign currency translation gain / (loss), net of deferred income tax recovery of $nil (2024 – 13</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -31454,14 +31452,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S236" s="5" t="n">
-        <v>0.0007739999999999999</v>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T236" s="5" t="n">
-        <v>0.009919000000000001</v>
+        <v>0.00512</v>
       </c>
       <c r="U236" s="5" t="n">
-        <v>-0.017742</v>
+        <v>-0.003421</v>
       </c>
     </row>
     <row r="237">
@@ -31477,7 +31477,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Comprehensive income $</t>
+          <t>deferred income tax expense of $369) total</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -31552,13 +31552,13 @@
         </is>
       </c>
       <c r="S237" s="5" t="n">
-        <v>0.030208</v>
+        <v>0.0007739999999999999</v>
       </c>
       <c r="T237" s="5" t="n">
-        <v>0.031657</v>
+        <v>0.009919000000000001</v>
       </c>
       <c r="U237" s="5" t="n">
-        <v>0.031231</v>
+        <v>-0.017742</v>
       </c>
     </row>
     <row r="238">
@@ -31569,12 +31569,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Unrealized foreign currency translation gain / (loss), net</t>
+          <t>deferred income tax expense of $369)</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Unrealized foreign currency translation gain / (loss), net of deferred income tax recovery of $369 (2023 – 11</t>
+          <t>Comprehensive income $</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -31649,15 +31649,13 @@
         </is>
       </c>
       <c r="S238" s="5" t="n">
-        <v>-0.001748</v>
+        <v>0.030208</v>
       </c>
       <c r="T238" s="5" t="n">
-        <v>0.00512</v>
-      </c>
-      <c r="U238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.031657</v>
+      </c>
+      <c r="U238" s="5" t="n">
+        <v>0.031231</v>
       </c>
     </row>
     <row r="239">
@@ -31668,12 +31666,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Other comprehensive income / (loss)</t>
+          <t>Unrealized foreign currency translation gain / (loss), net</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Gain / (loss) on revaluation of land and roads, net of deferred income tax expense of $1,027 (2022 –</t>
+          <t>Unrealized foreign currency translation gain / (loss), net of deferred income tax recovery of $369 (2023 – 11</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -31742,16 +31740,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R239" s="5" t="n">
-        <v>-0.010293</v>
+      <c r="R239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S239" s="5" t="n">
-        <v>0.002522</v>
-      </c>
-      <c r="T239" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.001748</v>
+      </c>
+      <c r="T239" s="5" t="n">
+        <v>0.00512</v>
       </c>
       <c r="U239" t="inlineStr">
         <is>
@@ -31767,12 +31765,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Unrealized foreign currency translation (loss) / gain, net</t>
+          <t>Other comprehensive income / (loss)</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Unrealized foreign currency translation (loss) / gain, net</t>
+          <t>Gain / (loss) on revaluation of land and roads, net of deferred income tax expense of $1,027 (2022 –</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -31842,10 +31840,10 @@
         </is>
       </c>
       <c r="R240" s="5" t="n">
-        <v>0.003121</v>
+        <v>-0.010293</v>
       </c>
       <c r="S240" s="5" t="n">
-        <v>-0.001748</v>
+        <v>0.002522</v>
       </c>
       <c r="T240" t="inlineStr">
         <is>
@@ -31871,7 +31869,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Unrealized foreign currency translation (loss) / gain, net total</t>
+          <t>Unrealized foreign currency translation (loss) / gain, net</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -31941,10 +31939,10 @@
         </is>
       </c>
       <c r="R241" s="5" t="n">
-        <v>-0.007172</v>
+        <v>0.003121</v>
       </c>
       <c r="S241" s="5" t="n">
-        <v>0.0007739999999999999</v>
+        <v>-0.001748</v>
       </c>
       <c r="T241" t="inlineStr">
         <is>
@@ -31970,7 +31968,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Comprehensive income $</t>
+          <t>Unrealized foreign currency translation (loss) / gain, net total</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -32040,10 +32038,10 @@
         </is>
       </c>
       <c r="R242" s="5" t="n">
-        <v>0.028335</v>
+        <v>-0.007172</v>
       </c>
       <c r="S242" s="5" t="n">
-        <v>0.030208</v>
+        <v>0.0007739999999999999</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -32064,12 +32062,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Other comprehensive income / (loss)</t>
+          <t>Unrealized foreign currency translation (loss) / gain, net</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Loss on revaluation of land and roads, net of deferred income tax recovery of $4,088 (2021 – deferred income</t>
+          <t>Comprehensive income $</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -32133,16 +32131,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q243" s="5" t="n">
-        <v>-0.000483</v>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R243" s="5" t="n">
-        <v>-0.010293</v>
-      </c>
-      <c r="S243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.028335</v>
+      </c>
+      <c r="S243" s="5" t="n">
+        <v>0.030208</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -32163,12 +32161,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>tax recovery of $62)</t>
+          <t>Other comprehensive income / (loss)</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Unrealized foreign currency translation gain / (loss)</t>
+          <t>Loss on revaluation of land and roads, net of deferred income tax recovery of $4,088 (2021 – deferred income</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
@@ -32233,10 +32231,10 @@
         </is>
       </c>
       <c r="Q244" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.000483</v>
       </c>
       <c r="R244" s="5" t="n">
-        <v>0.003121</v>
+        <v>-0.010293</v>
       </c>
       <c r="S244" t="inlineStr">
         <is>
@@ -32267,7 +32265,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>tax recovery of $62) total</t>
+          <t>Unrealized foreign currency translation gain / (loss)</t>
         </is>
       </c>
       <c r="D245" t="inlineStr"/>
@@ -32332,10 +32330,10 @@
         </is>
       </c>
       <c r="Q245" s="5" t="n">
-        <v>-0.001083</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="R245" s="5" t="n">
-        <v>-0.007172</v>
+        <v>0.003121</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
@@ -32366,7 +32364,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Comprehensive income $</t>
+          <t>tax recovery of $62) total</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
@@ -32431,10 +32429,10 @@
         </is>
       </c>
       <c r="Q246" s="5" t="n">
-        <v>0.017601</v>
+        <v>-0.001083</v>
       </c>
       <c r="R246" s="5" t="n">
-        <v>0.028335</v>
+        <v>-0.007172</v>
       </c>
       <c r="S246" t="inlineStr">
         <is>
@@ -32460,19 +32458,15 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Other comprehensive {loss) / income</t>
+          <t>tax recovery of $62)</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Deferred income tax (expense) / recovery</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Comprehensive income $</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>
@@ -32523,21 +32517,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O247" s="5" t="n">
-        <v>0.001459</v>
-      </c>
-      <c r="P247" s="5" t="n">
-        <v>-0.002184</v>
-      </c>
-      <c r="Q247" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R247" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q247" s="5" t="n">
+        <v>0.017601</v>
+      </c>
+      <c r="R247" s="5" t="n">
+        <v>0.028335</v>
       </c>
       <c r="S247" t="inlineStr">
         <is>
@@ -32568,10 +32562,14 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Gain / (loss) on revaluation of land and roads</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr"/>
+          <t>Deferred income tax (expense) / recovery</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -32623,10 +32621,10 @@
         </is>
       </c>
       <c r="O248" s="5" t="n">
-        <v>-0.005064</v>
+        <v>0.001459</v>
       </c>
       <c r="P248" s="5" t="n">
-        <v>0.007591</v>
+        <v>-0.002184</v>
       </c>
       <c r="Q248" t="inlineStr">
         <is>
@@ -32667,7 +32665,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Unrealized foreign currency translation (loss) / gain</t>
+          <t>Gain / (loss) on revaluation of land and roads</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
@@ -32722,10 +32720,10 @@
         </is>
       </c>
       <c r="O249" s="5" t="n">
-        <v>0.011007</v>
+        <v>-0.005064</v>
       </c>
       <c r="P249" s="5" t="n">
-        <v>-0.007048</v>
+        <v>0.007591</v>
       </c>
       <c r="Q249" t="inlineStr">
         <is>
@@ -32766,7 +32764,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Other comprehensive {loss) / income total</t>
+          <t>Unrealized foreign currency translation (loss) / gain</t>
         </is>
       </c>
       <c r="D250" t="inlineStr"/>
@@ -32821,10 +32819,10 @@
         </is>
       </c>
       <c r="O250" s="5" t="n">
-        <v>0.007402</v>
+        <v>0.011007</v>
       </c>
       <c r="P250" s="5" t="n">
-        <v>-0.001641</v>
+        <v>-0.007048</v>
       </c>
       <c r="Q250" t="inlineStr">
         <is>
@@ -32865,7 +32863,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Comprehensive income $</t>
+          <t>Other comprehensive {loss) / income total</t>
         </is>
       </c>
       <c r="D251" t="inlineStr"/>
@@ -32920,10 +32918,10 @@
         </is>
       </c>
       <c r="O251" s="5" t="n">
-        <v>0.033666</v>
+        <v>0.007402</v>
       </c>
       <c r="P251" s="5" t="n">
-        <v>0.015684</v>
+        <v>-0.001641</v>
       </c>
       <c r="Q251" t="inlineStr">
         <is>
@@ -32959,12 +32957,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Other comprehensive income / (loss)</t>
+          <t>Other comprehensive {loss) / income</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Deferred tax recovery</t>
+          <t>Comprehensive income $</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
@@ -33013,16 +33011,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N252" s="5" t="n">
-        <v>0.003322</v>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O252" s="5" t="n">
-        <v>0.001459</v>
-      </c>
-      <c r="P252" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.033666</v>
+      </c>
+      <c r="P252" s="5" t="n">
+        <v>0.015684</v>
       </c>
       <c r="Q252" t="inlineStr">
         <is>
@@ -33063,7 +33061,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Loss on revaluation of land and roads</t>
+          <t>Deferred tax recovery</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
@@ -33113,10 +33111,10 @@
         </is>
       </c>
       <c r="N253" s="5" t="n">
-        <v>-0.000673</v>
+        <v>0.003322</v>
       </c>
       <c r="O253" s="5" t="n">
-        <v>-0.005064</v>
+        <v>0.001459</v>
       </c>
       <c r="P253" t="inlineStr">
         <is>
@@ -33162,7 +33160,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Unrealized foreign currency translation gain / (loss)</t>
+          <t>Loss on revaluation of land and roads</t>
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
@@ -33212,10 +33210,10 @@
         </is>
       </c>
       <c r="N254" s="5" t="n">
-        <v>-0.008829999999999999</v>
+        <v>-0.000673</v>
       </c>
       <c r="O254" s="5" t="n">
-        <v>0.011007</v>
+        <v>-0.005064</v>
       </c>
       <c r="P254" t="inlineStr">
         <is>
@@ -33261,7 +33259,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Comprehensive income $</t>
+          <t>Unrealized foreign currency translation gain / (loss)</t>
         </is>
       </c>
       <c r="D255" t="inlineStr"/>
@@ -33290,23 +33288,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J255" s="5" t="n">
-        <v>0.011995</v>
-      </c>
-      <c r="K255" s="5" t="n">
-        <v>0.080223</v>
-      </c>
-      <c r="L255" s="5" t="n">
-        <v>0.03391</v>
-      </c>
-      <c r="M255" s="5" t="n">
-        <v>0.017536</v>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N255" s="5" t="n">
-        <v>0.024638</v>
+        <v>-0.008829999999999999</v>
       </c>
       <c r="O255" s="5" t="n">
-        <v>0.033666</v>
+        <v>0.011007</v>
       </c>
       <c r="P255" t="inlineStr">
         <is>
@@ -33352,7 +33358,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Gain / (loss) on revaluation of land and roads 5</t>
+          <t>Comprehensive income $</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
@@ -33381,31 +33387,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J256" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K256" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J256" s="5" t="n">
+        <v>0.011995</v>
+      </c>
+      <c r="K256" s="5" t="n">
+        <v>0.080223</v>
       </c>
       <c r="L256" s="5" t="n">
-        <v>-0.003173</v>
+        <v>0.03391</v>
       </c>
       <c r="M256" s="5" t="n">
-        <v>0.005692</v>
-      </c>
-      <c r="N256" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O256" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.017536</v>
+      </c>
+      <c r="N256" s="5" t="n">
+        <v>0.024638</v>
+      </c>
+      <c r="O256" s="5" t="n">
+        <v>0.033666</v>
       </c>
       <c r="P256" t="inlineStr">
         <is>
@@ -33451,7 +33449,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Unrealized foreign currency translation (loss) / gain</t>
+          <t>Deferred tax recovery / (expense)</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
@@ -33490,16 +33488,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L257" s="5" t="n">
-        <v>0.023683</v>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M257" s="5" t="n">
-        <v>-0.004228</v>
-      </c>
-      <c r="N257" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.003748</v>
+      </c>
+      <c r="N257" s="5" t="n">
+        <v>0.003322</v>
       </c>
       <c r="O257" t="inlineStr">
         <is>
@@ -33550,7 +33548,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Amortization of derivatives designated as cash flow hedges 11</t>
+          <t>(Loss) / gain on revaluation of land and roads</t>
         </is>
       </c>
       <c r="D258" t="inlineStr"/>
@@ -33579,24 +33577,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J258" s="5" t="n">
-        <v>-0.000189</v>
-      </c>
-      <c r="K258" s="5" t="n">
-        <v>-0.000188</v>
-      </c>
-      <c r="L258" s="5" t="n">
-        <v>-0.000241</v>
-      </c>
-      <c r="M258" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N258" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M258" s="5" t="n">
+        <v>0.009254</v>
+      </c>
+      <c r="N258" s="5" t="n">
+        <v>-0.000673</v>
       </c>
       <c r="O258" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>(Loss) / gain on revaluation of land and roads 5</t>
+          <t>Unrealized foreign currency translation loss</t>
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
@@ -33681,21 +33681,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K259" s="5" t="n">
-        <v>0.027981</v>
-      </c>
-      <c r="L259" s="5" t="n">
-        <v>-0.003173</v>
-      </c>
-      <c r="M259" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N259" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M259" s="5" t="n">
+        <v>-0.004312</v>
+      </c>
+      <c r="N259" s="5" t="n">
+        <v>-0.008829999999999999</v>
       </c>
       <c r="O259" t="inlineStr">
         <is>
@@ -33746,7 +33746,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Unrealized foreign currency translation gain</t>
+          <t>Gain / (loss) on revaluation of land and roads 5</t>
         </is>
       </c>
       <c r="D260" t="inlineStr"/>
@@ -33780,16 +33780,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K260" s="5" t="n">
-        <v>0.009192000000000001</v>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L260" s="5" t="n">
-        <v>0.023683</v>
-      </c>
-      <c r="M260" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.003173</v>
+      </c>
+      <c r="M260" s="5" t="n">
+        <v>0.005692</v>
       </c>
       <c r="N260" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Gain / (loss) on revaluation of roads and land 5</t>
+          <t>Unrealized foreign currency translation (loss) / gain</t>
         </is>
       </c>
       <c r="D261" t="inlineStr"/>
@@ -33874,21 +33874,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J261" s="5" t="n">
-        <v>-0.001215</v>
-      </c>
-      <c r="K261" s="5" t="n">
-        <v>0.027981</v>
-      </c>
-      <c r="L261" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M261" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L261" s="5" t="n">
+        <v>0.023683</v>
+      </c>
+      <c r="M261" s="5" t="n">
+        <v>-0.004228</v>
       </c>
       <c r="N261" t="inlineStr">
         <is>
@@ -33944,7 +33944,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Unrealized foreign currency translation income gain</t>
+          <t>Amortization of derivatives designated as cash flow hedges 11</t>
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
@@ -33974,15 +33974,13 @@
         </is>
       </c>
       <c r="J262" s="5" t="n">
-        <v>0.006151</v>
+        <v>-0.000189</v>
       </c>
       <c r="K262" s="5" t="n">
-        <v>0.009192000000000001</v>
-      </c>
-      <c r="L262" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.000188</v>
+      </c>
+      <c r="L262" s="5" t="n">
+        <v>-0.000241</v>
       </c>
       <c r="M262" t="inlineStr">
         <is>
@@ -34038,12 +34036,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Other comprehensive income (loss)</t>
+          <t>Other comprehensive income / (loss)</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Gain (loss) on revaluation of roads and land 5</t>
+          <t>(Loss) / gain on revaluation of land and roads 5</t>
         </is>
       </c>
       <c r="D263" t="inlineStr"/>
@@ -34062,24 +34060,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H263" s="5" t="n">
-        <v>-0.000169</v>
-      </c>
-      <c r="I263" s="5" t="n">
-        <v>0.000413</v>
-      </c>
-      <c r="J263" s="5" t="n">
-        <v>-0.001215</v>
-      </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K263" s="5" t="n">
+        <v>0.027981</v>
+      </c>
+      <c r="L263" s="5" t="n">
+        <v>-0.003173</v>
       </c>
       <c r="M263" t="inlineStr">
         <is>
@@ -34135,12 +34135,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Other comprehensive income (loss)</t>
+          <t>Other comprehensive income / (loss)</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Unrealized foreign currency translation income gain (loss)</t>
+          <t>Unrealized foreign currency translation gain</t>
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
@@ -34164,21 +34164,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I264" s="5" t="n">
-        <v>-0.002499</v>
-      </c>
-      <c r="J264" s="5" t="n">
-        <v>0.006151</v>
-      </c>
-      <c r="K264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K264" s="5" t="n">
+        <v>0.009192000000000001</v>
+      </c>
+      <c r="L264" s="5" t="n">
+        <v>0.023683</v>
       </c>
       <c r="M264" t="inlineStr">
         <is>
@@ -34234,12 +34234,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Other comprehensive income (loss)</t>
+          <t>Other comprehensive income / (loss)</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Amortization of derivatives designated as cash flow hedges 11</t>
+          <t>Gain / (loss) on revaluation of roads and land 5</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
@@ -34258,19 +34258,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H265" s="5" t="n">
-        <v>-0.000321</v>
-      </c>
-      <c r="I265" s="5" t="n">
-        <v>-0.000195</v>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J265" s="5" t="n">
-        <v>-0.000189</v>
-      </c>
-      <c r="K265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.001215</v>
+      </c>
+      <c r="K265" s="5" t="n">
+        <v>0.027981</v>
       </c>
       <c r="L265" t="inlineStr">
         <is>
@@ -34331,12 +34333,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Other comprehensive income (loss)</t>
+          <t>Other comprehensive income / (loss)</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Comprehensive income $</t>
+          <t>Unrealized foreign currency translation income gain</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
@@ -34355,19 +34357,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H266" s="5" t="n">
-        <v>0.015828</v>
-      </c>
-      <c r="I266" s="5" t="n">
-        <v>0.011448</v>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J266" s="5" t="n">
-        <v>0.011995</v>
-      </c>
-      <c r="K266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.006151</v>
+      </c>
+      <c r="K266" s="5" t="n">
+        <v>0.009192000000000001</v>
       </c>
       <c r="L266" t="inlineStr">
         <is>
@@ -34433,7 +34437,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Unrealized foreign currency translation income (loss)</t>
+          <t>Gain (loss) on revaluation of roads and land 5</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -34453,15 +34457,13 @@
         </is>
       </c>
       <c r="H267" s="5" t="n">
-        <v>0.002559</v>
+        <v>-0.000169</v>
       </c>
       <c r="I267" s="5" t="n">
-        <v>-0.002499</v>
-      </c>
-      <c r="J267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000413</v>
+      </c>
+      <c r="J267" s="5" t="n">
+        <v>-0.001215</v>
       </c>
       <c r="K267" t="inlineStr">
         <is>
@@ -34525,10 +34527,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B268" t="inlineStr"/>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Other comprehensive income (loss)</t>
+        </is>
+      </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>For the Years Ended December</t>
+          <t>Unrealized foreign currency translation income gain (loss)</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -34547,18 +34553,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H268" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="I268" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J268" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I268" s="5" t="n">
+        <v>-0.002499</v>
+      </c>
+      <c r="J268" s="5" t="n">
+        <v>0.006151</v>
       </c>
       <c r="K268" t="inlineStr">
         <is>
@@ -34622,10 +34626,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr"/>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Other comprehensive income (loss)</t>
+        </is>
+      </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>(CAD thousands) Note 2011</t>
+          <t>Amortization of derivatives designated as cash flow hedges 11</t>
         </is>
       </c>
       <c r="D269" t="inlineStr"/>
@@ -34645,17 +34653,13 @@
         </is>
       </c>
       <c r="H269" s="5" t="n">
-        <v>0.020101</v>
-      </c>
-      <c r="I269" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J269" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.000321</v>
+      </c>
+      <c r="I269" s="5" t="n">
+        <v>-0.000195</v>
+      </c>
+      <c r="J269" s="5" t="n">
+        <v>-0.000189</v>
       </c>
       <c r="K269" t="inlineStr">
         <is>
@@ -34719,17 +34723,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr"/>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Other comprehensive income (loss)</t>
+        </is>
+      </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Net income $ 13,759 $</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Comprehensive income $</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr"/>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>
@@ -34746,17 +34750,13 @@
         </is>
       </c>
       <c r="H270" s="5" t="n">
-        <v>0.031306</v>
-      </c>
-      <c r="I270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.015828</v>
+      </c>
+      <c r="I270" s="5" t="n">
+        <v>0.011448</v>
+      </c>
+      <c r="J270" s="5" t="n">
+        <v>0.011995</v>
       </c>
       <c r="K270" t="inlineStr">
         <is>
@@ -34827,7 +34827,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Unrealized foreign currency translation income (loss) 2,559</t>
+          <t>Unrealized foreign currency translation income (loss)</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
@@ -34847,12 +34847,10 @@
         </is>
       </c>
       <c r="H271" s="5" t="n">
-        <v>-0.002917</v>
-      </c>
-      <c r="I271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002559</v>
+      </c>
+      <c r="I271" s="5" t="n">
+        <v>-0.002499</v>
       </c>
       <c r="J271" t="inlineStr">
         <is>
@@ -34921,14 +34919,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>Other comprehensive income (loss)</t>
-        </is>
-      </c>
+      <c r="B272" t="inlineStr"/>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Amortization of derivatives designated as cash flow hedges 12 (321)</t>
+          <t>For the Years Ended December</t>
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
@@ -34948,7 +34942,7 @@
         </is>
       </c>
       <c r="H272" s="5" t="n">
-        <v>0.001134</v>
+        <v>3.1e-05</v>
       </c>
       <c r="I272" t="inlineStr">
         <is>
@@ -35022,14 +35016,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>Other comprehensive income (loss)</t>
-        </is>
-      </c>
+      <c r="B273" t="inlineStr"/>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Gain (loss) on revaluation of roads and land 6 (169)</t>
+          <t>(CAD thousands) Note 2011</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
@@ -35049,7 +35039,7 @@
         </is>
       </c>
       <c r="H273" s="5" t="n">
-        <v>0.002354</v>
+        <v>0.020101</v>
       </c>
       <c r="I273" t="inlineStr">
         <is>
@@ -35123,17 +35113,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>Other comprehensive income (loss)</t>
-        </is>
-      </c>
+      <c r="B274" t="inlineStr"/>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Comprehensive income $ 15,828 $</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr"/>
+          <t>Net income $ 13,759 $</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
           <t>-</t>
@@ -35150,7 +35140,7 @@
         </is>
       </c>
       <c r="H274" s="5" t="n">
-        <v>0.031877</v>
+        <v>0.031306</v>
       </c>
       <c r="I274" t="inlineStr">
         <is>
@@ -35224,30 +35214,34 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr"/>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Other comprehensive income (loss)</t>
+        </is>
+      </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Net sales $</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E275" s="5" t="n">
-        <v>6.790000000000001e-05</v>
-      </c>
-      <c r="F275" s="5" t="n">
-        <v>6.34e-05</v>
-      </c>
-      <c r="G275" s="5" t="n">
-        <v>7.1e-05</v>
-      </c>
-      <c r="H275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Unrealized foreign currency translation income (loss) 2,559</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr"/>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H275" s="5" t="n">
+        <v>-0.002917</v>
       </c>
       <c r="I275" t="inlineStr">
         <is>
@@ -35323,32 +35317,32 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Other comprehensive income (loss)</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Cost of sales</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
-      <c r="E276" s="5" t="n">
-        <v>4.48e-05</v>
-      </c>
-      <c r="F276" s="5" t="n">
-        <v>4.33e-05</v>
-      </c>
-      <c r="G276" s="5" t="n">
-        <v>4.6e-05</v>
-      </c>
-      <c r="H276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Amortization of derivatives designated as cash flow hedges 12 (321)</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr"/>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H276" s="5" t="n">
+        <v>0.001134</v>
       </c>
       <c r="I276" t="inlineStr">
         <is>
@@ -35424,28 +35418,32 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Other comprehensive income (loss)</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Selling, administration and other</t>
+          <t>Gain (loss) on revaluation of roads and land 6 (169)</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
-      <c r="E277" s="5" t="n">
-        <v>6.400000000000001e-06</v>
-      </c>
-      <c r="F277" s="5" t="n">
-        <v>8.599999999999999e-06</v>
-      </c>
-      <c r="G277" s="5" t="n">
-        <v>7e-06</v>
-      </c>
-      <c r="H277" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H277" s="5" t="n">
+        <v>0.002354</v>
       </c>
       <c r="I277" t="inlineStr">
         <is>
@@ -35521,28 +35519,32 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Operating costs and expenses</t>
+          <t>Other comprehensive income (loss)</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Depreciation and depletion</t>
+          <t>Comprehensive income $ 15,828 $</t>
         </is>
       </c>
       <c r="D278" t="inlineStr"/>
-      <c r="E278" s="5" t="n">
-        <v>7.4e-06</v>
-      </c>
-      <c r="F278" s="5" t="n">
-        <v>7.1e-06</v>
-      </c>
-      <c r="G278" s="5" t="n">
-        <v>6.599999999999999e-06</v>
-      </c>
-      <c r="H278" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H278" s="5" t="n">
+        <v>0.031877</v>
       </c>
       <c r="I278" t="inlineStr">
         <is>
@@ -35616,29 +35618,25 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>Operating costs and expenses</t>
-        </is>
-      </c>
+      <c r="B279" t="inlineStr"/>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Operating costs and expenses total</t>
+          <t>Net sales $</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>TotalRevenue</t>
         </is>
       </c>
       <c r="E279" s="5" t="n">
-        <v>5.86e-05</v>
+        <v>6.790000000000001e-05</v>
       </c>
       <c r="F279" s="5" t="n">
-        <v>5.9e-05</v>
+        <v>6.34e-05</v>
       </c>
       <c r="G279" s="5" t="n">
-        <v>5.96e-05</v>
+        <v>7.1e-05</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
@@ -35724,22 +35722,22 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Operating earnings</t>
+          <t>Cost of sales</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
+          <t>CostOfRevenue</t>
         </is>
       </c>
       <c r="E280" s="5" t="n">
-        <v>9.300000000000001e-06</v>
+        <v>4.48e-05</v>
       </c>
       <c r="F280" s="5" t="n">
-        <v>4.4e-06</v>
+        <v>4.33e-05</v>
       </c>
       <c r="G280" s="5" t="n">
-        <v>1.14e-05</v>
+        <v>4.6e-05</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
@@ -35825,20 +35823,18 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Gain on sale of timberlands 8</t>
+          <t>Selling, administration and other</t>
         </is>
       </c>
       <c r="D281" t="inlineStr"/>
       <c r="E281" s="5" t="n">
-        <v>-7e-07</v>
+        <v>6.400000000000001e-06</v>
       </c>
       <c r="F281" s="5" t="n">
-        <v>-6e-07</v>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>8.599999999999999e-06</v>
+      </c>
+      <c r="G281" s="5" t="n">
+        <v>7e-06</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -35924,20 +35920,18 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Gain on Class B Interest Liability of a subsidiary 6</t>
+          <t>Depreciation and depletion</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
       <c r="E282" s="5" t="n">
-        <v>-2.22e-05</v>
+        <v>7.4e-06</v>
       </c>
       <c r="F282" s="5" t="n">
-        <v>-4.7e-06</v>
-      </c>
-      <c r="G282" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7.1e-06</v>
+      </c>
+      <c r="G282" s="5" t="n">
+        <v>6.599999999999999e-06</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
@@ -36018,27 +36012,27 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Interest</t>
+          <t>Operating costs and expenses</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Interest expense 5</t>
+          <t>Operating costs and expenses total</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>InterestExpenseOperating</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E283" s="5" t="n">
-        <v>3.6e-06</v>
+        <v>5.86e-05</v>
       </c>
       <c r="F283" s="5" t="n">
-        <v>3.1e-06</v>
+        <v>5.9e-05</v>
       </c>
       <c r="G283" s="5" t="n">
-        <v>3.8e-06</v>
+        <v>5.96e-05</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
@@ -36119,25 +36113,27 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Interest</t>
+          <t>Operating costs and expenses</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Class B Interest Liability of a subsidiary 6</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr"/>
+          <t>Operating earnings</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E284" s="5" t="n">
-        <v>3.7e-06</v>
+        <v>9.300000000000001e-06</v>
       </c>
       <c r="F284" s="5" t="n">
-        <v>3e-07</v>
-      </c>
-      <c r="G284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.4e-06</v>
+      </c>
+      <c r="G284" s="5" t="n">
+        <v>1.14e-05</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
@@ -36218,25 +36214,25 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Interest</t>
+          <t>Operating costs and expenses</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Earnings before income tax recovery</t>
+          <t>Gain on sale of timberlands 8</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
-      <c r="E285" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E285" s="5" t="n">
+        <v>-7e-07</v>
       </c>
       <c r="F285" s="5" t="n">
-        <v>6.3e-06</v>
-      </c>
-      <c r="G285" s="5" t="n">
-        <v>7.599999999999999e-06</v>
+        <v>-6e-07</v>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -36317,25 +36313,25 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Interest</t>
+          <t>Operating costs and expenses</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Future income tax recovery 12</t>
+          <t>Gain on Class B Interest Liability of a subsidiary 6</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
-      <c r="E286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E286" s="5" t="n">
+        <v>-2.22e-05</v>
       </c>
       <c r="F286" s="5" t="n">
-        <v>3e-06</v>
-      </c>
-      <c r="G286" s="5" t="n">
-        <v>1.2e-06</v>
+        <v>-4.7e-06</v>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -36421,22 +36417,22 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Net income for the year</t>
+          <t>Interest expense 5</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E287" s="5" t="n">
-        <v>1.89e-05</v>
+        <v>3.6e-06</v>
       </c>
       <c r="F287" s="5" t="n">
-        <v>9.300000000000001e-06</v>
+        <v>3.1e-06</v>
       </c>
       <c r="G287" s="5" t="n">
-        <v>8.8e-06</v>
+        <v>3.8e-06</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
@@ -36522,18 +36518,20 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Deﬁ cit, beginning of year</t>
+          <t>Class B Interest Liability of a subsidiary 6</t>
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
       <c r="E288" s="5" t="n">
-        <v>-2.98e-05</v>
+        <v>3.7e-06</v>
       </c>
       <c r="F288" s="5" t="n">
-        <v>-2.09e-05</v>
-      </c>
-      <c r="G288" s="5" t="n">
-        <v>-2.3e-05</v>
+        <v>3e-07</v>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
@@ -36619,20 +36617,24 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Shareholders’ dividends declared 14</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr"/>
+          <t>Earnings before income tax recovery</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E289" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F289" s="5" t="n">
-        <v>-1.14e-05</v>
+        <v>6.3e-06</v>
       </c>
       <c r="G289" s="5" t="n">
-        <v>-3.6e-06</v>
+        <v>7.599999999999999e-06</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -36718,18 +36720,24 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Deﬁ cit, end of year $</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr"/>
-      <c r="E290" s="5" t="n">
-        <v>-2.09e-05</v>
+          <t>Future income tax recovery 12</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F290" s="5" t="n">
-        <v>-2.3e-05</v>
+        <v>3e-06</v>
       </c>
       <c r="G290" s="5" t="n">
-        <v>-1.78e-05</v>
+        <v>1.2e-06</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -36815,24 +36823,22 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Net income per share – basic 7 $</t>
+          <t>Net income for the year</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E291" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E291" s="5" t="n">
+        <v>1.89e-05</v>
       </c>
       <c r="F291" s="5" t="n">
-        <v>5.8e-07</v>
+        <v>9.300000000000001e-06</v>
       </c>
       <c r="G291" s="5" t="n">
-        <v>5.3e-07</v>
+        <v>8.8e-06</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
@@ -36918,24 +36924,18 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Net income per share – diluted 7 $</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr">
-        <is>
-          <t>DilutedEPS</t>
-        </is>
-      </c>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Deﬁ cit, beginning of year</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr"/>
+      <c r="E292" s="5" t="n">
+        <v>-2.98e-05</v>
       </c>
       <c r="F292" s="5" t="n">
-        <v>3e-07</v>
+        <v>-2.09e-05</v>
       </c>
       <c r="G292" s="5" t="n">
-        <v>5.3e-07</v>
+        <v>-2.3e-05</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
@@ -37021,26 +37021,20 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
-      <c r="E293" s="5" t="n">
-        <v>-2e-07</v>
-      </c>
-      <c r="F293" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G293" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Shareholders’ dividends declared 14</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr"/>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F293" s="5" t="n">
+        <v>-1.14e-05</v>
+      </c>
+      <c r="G293" s="5" t="n">
+        <v>-3.6e-06</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
@@ -37126,20 +37120,18 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Earnings before income tax recovery (expense)</t>
+          <t>Deﬁ cit, end of year $</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
       <c r="E294" s="5" t="n">
-        <v>2.51e-05</v>
+        <v>-2.09e-05</v>
       </c>
       <c r="F294" s="5" t="n">
-        <v>6.3e-06</v>
-      </c>
-      <c r="G294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.3e-05</v>
+      </c>
+      <c r="G294" s="5" t="n">
+        <v>-1.78e-05</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
@@ -37225,20 +37217,24 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Future income tax recovery (expense) 12</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr"/>
-      <c r="E295" s="5" t="n">
-        <v>-6.2e-06</v>
+          <t>Net income per share – basic 7 $</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F295" s="5" t="n">
-        <v>3e-06</v>
-      </c>
-      <c r="G295" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.8e-07</v>
+      </c>
+      <c r="G295" s="5" t="n">
+        <v>5.3e-07</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
@@ -37324,20 +37320,24 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Unitholders’ distributions 14</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr"/>
-      <c r="E296" s="5" t="n">
-        <v>-1e-05</v>
+          <t>Net income per share – diluted 7 $</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>DilutedEPS</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F296" s="5" t="n">
-        <v>-1.14e-05</v>
-      </c>
-      <c r="G296" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3e-07</v>
+      </c>
+      <c r="G296" s="5" t="n">
+        <v>5.3e-07</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
@@ -37423,15 +37423,21 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Net income per unit – basic 7 $</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E297" s="5" t="n">
-        <v>1.57e-06</v>
-      </c>
-      <c r="F297" s="5" t="n">
-        <v>5.8e-07</v>
+        <v>-2e-07</v>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
@@ -37522,87 +37528,491 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
+          <t>Earnings before income tax recovery (expense)</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E298" s="5" t="n">
+        <v>2.51e-05</v>
+      </c>
+      <c r="F298" s="5" t="n">
+        <v>6.3e-06</v>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Interest</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Future income tax recovery (expense) 12</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E299" s="5" t="n">
+        <v>-6.2e-06</v>
+      </c>
+      <c r="F299" s="5" t="n">
+        <v>3e-06</v>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Interest</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Unitholders’ distributions 14</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr"/>
+      <c r="E300" s="5" t="n">
+        <v>-1e-05</v>
+      </c>
+      <c r="F300" s="5" t="n">
+        <v>-1.14e-05</v>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Interest</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Net income per unit – basic 7 $</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr"/>
+      <c r="E301" s="5" t="n">
+        <v>1.57e-06</v>
+      </c>
+      <c r="F301" s="5" t="n">
+        <v>5.8e-07</v>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Interest</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
           <t>Net income per unit – diluted 7 $</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr"/>
-      <c r="E298" s="5" t="n">
+      <c r="D302" t="inlineStr"/>
+      <c r="E302" s="5" t="n">
         <v>2e-08</v>
       </c>
-      <c r="F298" s="5" t="n">
+      <c r="F302" s="5" t="n">
         <v>3e-07</v>
       </c>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U298" t="inlineStr">
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U302" t="inlineStr">
         <is>
           <t>-</t>
         </is>
